--- a/Proyecto Interno/interno/output/gabas/gaba_exchanges_adj.xlsx
+++ b/Proyecto Interno/interno/output/gabas/gaba_exchanges_adj.xlsx
@@ -4555,13 +4555,13 @@
         <v>243.94</v>
       </c>
       <c r="H100">
-        <v>1.100735103319239</v>
+        <v>1.102250382477939</v>
       </c>
       <c r="I100">
-        <v>3.302205309957718</v>
+        <v>3.306751147433818</v>
       </c>
       <c r="J100">
-        <v>268.5133211036953</v>
+        <v>268.8829583016686</v>
       </c>
     </row>
     <row r="101">
@@ -4597,13 +4597,13 @@
         <v>571</v>
       </c>
       <c r="H101">
-        <v>1.100735103319239</v>
+        <v>1.102250382477939</v>
       </c>
       <c r="I101">
-        <v>8.255513274894296</v>
+        <v>8.266877868584546</v>
       </c>
       <c r="J101">
-        <v>628.5197439952857</v>
+        <v>629.3849683949035</v>
       </c>
     </row>
     <row r="102">
@@ -4639,13 +4639,13 @@
         <v>726</v>
       </c>
       <c r="H102">
-        <v>1.100735103319239</v>
+        <v>1.102250382477939</v>
       </c>
       <c r="I102">
-        <v>8.805880826553915</v>
+        <v>8.818003059823516</v>
       </c>
       <c r="J102">
-        <v>799.1336850097678</v>
+        <v>800.2337776789841</v>
       </c>
     </row>
     <row r="103">
@@ -4681,13 +4681,13 @@
         <v>221</v>
       </c>
       <c r="H103">
-        <v>1.100735103319239</v>
+        <v>1.102250382477939</v>
       </c>
       <c r="I103">
-        <v>5.503675516596197</v>
+        <v>5.511251912389698</v>
       </c>
       <c r="J103">
-        <v>243.2624578335519</v>
+        <v>243.5973345276246</v>
       </c>
     </row>
     <row r="104">
@@ -4723,13 +4723,13 @@
         <v>537</v>
       </c>
       <c r="H104">
-        <v>1.100735103319239</v>
+        <v>1.102250382477939</v>
       </c>
       <c r="I104">
-        <v>5.503675516596197</v>
+        <v>5.511251912389698</v>
       </c>
       <c r="J104">
-        <v>591.0947504824316</v>
+        <v>591.9084553906536</v>
       </c>
     </row>
     <row r="105">
@@ -4765,13 +4765,13 @@
         <v>98</v>
       </c>
       <c r="H105">
-        <v>1.100735103319239</v>
+        <v>1.102250382477939</v>
       </c>
       <c r="I105">
-        <v>2.751837758298099</v>
+        <v>2.755625956194849</v>
       </c>
       <c r="J105">
-        <v>107.8720401252855</v>
+        <v>108.0205374828381</v>
       </c>
     </row>
     <row r="106">
@@ -4807,13 +4807,13 @@
         <v>98</v>
       </c>
       <c r="H106">
-        <v>1.100735103319239</v>
+        <v>1.102250382477939</v>
       </c>
       <c r="I106">
-        <v>2.751837758298099</v>
+        <v>2.755625956194849</v>
       </c>
       <c r="J106">
-        <v>107.8720401252855</v>
+        <v>108.0205374828381</v>
       </c>
     </row>
     <row r="107">
@@ -5731,13 +5731,13 @@
         <v>243.94</v>
       </c>
       <c r="H128">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I128">
-        <v>3.25045792814944</v>
+        <v>3.251896062569442</v>
       </c>
       <c r="J128">
-        <v>264.3055689975914</v>
+        <v>264.4225085010632</v>
       </c>
     </row>
     <row r="129">
@@ -5773,13 +5773,13 @@
         <v>571</v>
       </c>
       <c r="H129">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I129">
-        <v>8.126144820373598</v>
+        <v>8.129740156423605</v>
       </c>
       <c r="J129">
-        <v>618.6704923244433</v>
+        <v>618.9442172423838</v>
       </c>
     </row>
     <row r="130">
@@ -5815,13 +5815,13 @@
         <v>726</v>
       </c>
       <c r="H130">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I130">
-        <v>8.667887808398506</v>
+        <v>8.671722833518512</v>
       </c>
       <c r="J130">
-        <v>786.6108186121644</v>
+        <v>786.958847141805</v>
       </c>
     </row>
     <row r="131">
@@ -5857,13 +5857,13 @@
         <v>221</v>
       </c>
       <c r="H131">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I131">
-        <v>5.417429880249066</v>
+        <v>5.41982677094907</v>
       </c>
       <c r="J131">
-        <v>239.4504007070087</v>
+        <v>239.5563432759489</v>
       </c>
     </row>
     <row r="132">
@@ -5899,13 +5899,13 @@
         <v>537</v>
       </c>
       <c r="H132">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I132">
-        <v>5.417429880249066</v>
+        <v>5.41982677094907</v>
       </c>
       <c r="J132">
-        <v>581.8319691387497</v>
+        <v>582.0893951999301</v>
       </c>
     </row>
     <row r="133">
@@ -5941,13 +5941,13 @@
         <v>98</v>
       </c>
       <c r="H133">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I133">
-        <v>2.708714940124533</v>
+        <v>2.709913385474535</v>
       </c>
       <c r="J133">
-        <v>106.1816256528817</v>
+        <v>106.2286047106018</v>
       </c>
     </row>
     <row r="134">
@@ -5983,13 +5983,13 @@
         <v>98</v>
       </c>
       <c r="H134">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I134">
-        <v>2.708714940124533</v>
+        <v>2.709913385474535</v>
       </c>
       <c r="J134">
-        <v>106.1816256528817</v>
+        <v>106.2286047106018</v>
       </c>
     </row>
     <row r="135">
@@ -7495,13 +7495,13 @@
         <v>243.94</v>
       </c>
       <c r="H170">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I170">
-        <v>3.25045792814944</v>
+        <v>3.251896062569442</v>
       </c>
       <c r="J170">
-        <v>264.3055689975914</v>
+        <v>264.4225085010632</v>
       </c>
     </row>
     <row r="171">
@@ -7537,13 +7537,13 @@
         <v>571</v>
       </c>
       <c r="H171">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I171">
-        <v>8.126144820373598</v>
+        <v>8.129740156423605</v>
       </c>
       <c r="J171">
-        <v>618.6704923244433</v>
+        <v>618.9442172423838</v>
       </c>
     </row>
     <row r="172">
@@ -7579,13 +7579,13 @@
         <v>726</v>
       </c>
       <c r="H172">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I172">
-        <v>8.667887808398506</v>
+        <v>8.671722833518512</v>
       </c>
       <c r="J172">
-        <v>786.6108186121644</v>
+        <v>786.958847141805</v>
       </c>
     </row>
     <row r="173">
@@ -7621,13 +7621,13 @@
         <v>221</v>
       </c>
       <c r="H173">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I173">
-        <v>5.417429880249066</v>
+        <v>5.41982677094907</v>
       </c>
       <c r="J173">
-        <v>239.4504007070087</v>
+        <v>239.5563432759489</v>
       </c>
     </row>
     <row r="174">
@@ -7663,13 +7663,13 @@
         <v>537</v>
       </c>
       <c r="H174">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I174">
-        <v>5.417429880249066</v>
+        <v>5.41982677094907</v>
       </c>
       <c r="J174">
-        <v>581.8319691387497</v>
+        <v>582.0893951999301</v>
       </c>
     </row>
     <row r="175">
@@ -7705,13 +7705,13 @@
         <v>98</v>
       </c>
       <c r="H175">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I175">
-        <v>2.708714940124533</v>
+        <v>2.709913385474535</v>
       </c>
       <c r="J175">
-        <v>106.1816256528817</v>
+        <v>106.2286047106018</v>
       </c>
     </row>
     <row r="176">
@@ -7747,13 +7747,13 @@
         <v>98</v>
       </c>
       <c r="H176">
-        <v>1.083485976049813</v>
+        <v>1.083965354189814</v>
       </c>
       <c r="I176">
-        <v>2.708714940124533</v>
+        <v>2.709913385474535</v>
       </c>
       <c r="J176">
-        <v>106.1816256528817</v>
+        <v>106.2286047106018</v>
       </c>
     </row>
     <row r="177">
@@ -7789,13 +7789,13 @@
         <v>243.95</v>
       </c>
       <c r="H177">
-        <v>1.009073871875007</v>
+        <v>1.009245509561976</v>
       </c>
       <c r="I177">
-        <v>3.02722161562502</v>
+        <v>3.027736528685928</v>
       </c>
       <c r="J177">
-        <v>246.1635710439079</v>
+        <v>246.2054420576441</v>
       </c>
     </row>
     <row r="178">
@@ -7831,13 +7831,13 @@
         <v>492</v>
       </c>
       <c r="H178">
-        <v>1.009073871875007</v>
+        <v>1.009245509561976</v>
       </c>
       <c r="I178">
-        <v>6.558980167187544</v>
+        <v>6.560095812152845</v>
       </c>
       <c r="J178">
-        <v>496.4643449625033</v>
+        <v>496.5487907044923</v>
       </c>
     </row>
     <row r="179">
@@ -7873,13 +7873,13 @@
         <v>545</v>
       </c>
       <c r="H179">
-        <v>1.009073871875007</v>
+        <v>1.009245509561976</v>
       </c>
       <c r="I179">
-        <v>6.05444323125004</v>
+        <v>6.055473057371857</v>
       </c>
       <c r="J179">
-        <v>549.9452601718787</v>
+        <v>550.038802711277</v>
       </c>
     </row>
     <row r="180">
@@ -7915,13 +7915,13 @@
         <v>177</v>
       </c>
       <c r="H180">
-        <v>1.009073871875007</v>
+        <v>1.009245509561976</v>
       </c>
       <c r="I180">
-        <v>4.036295487500027</v>
+        <v>4.036982038247904</v>
       </c>
       <c r="J180">
-        <v>178.6060753218762</v>
+        <v>178.6364551924698</v>
       </c>
     </row>
     <row r="181">
@@ -7957,13 +7957,13 @@
         <v>376</v>
       </c>
       <c r="H181">
-        <v>1.009073871875007</v>
+        <v>1.009245509561976</v>
       </c>
       <c r="I181">
-        <v>3.531758551562524</v>
+        <v>3.532359283466916</v>
       </c>
       <c r="J181">
-        <v>379.4117758250026</v>
+        <v>379.476311595303</v>
       </c>
     </row>
     <row r="182">
@@ -7999,13 +7999,13 @@
         <v>78.5</v>
       </c>
       <c r="H182">
-        <v>1.009073871875007</v>
+        <v>1.009245509561976</v>
       </c>
       <c r="I182">
-        <v>2.018147743750013</v>
+        <v>2.018491019123952</v>
       </c>
       <c r="J182">
-        <v>79.21229894218803</v>
+        <v>79.22577250061512</v>
       </c>
     </row>
     <row r="183">
@@ -8041,13 +8041,13 @@
         <v>78.5</v>
       </c>
       <c r="H183">
-        <v>1.009073871875007</v>
+        <v>1.009245509561976</v>
       </c>
       <c r="I183">
-        <v>2.018147743750013</v>
+        <v>2.018491019123952</v>
       </c>
       <c r="J183">
-        <v>79.21229894218803</v>
+        <v>79.22577250061512</v>
       </c>
     </row>
     <row r="184">
@@ -8083,13 +8083,13 @@
         <v>243.94</v>
       </c>
       <c r="H184">
-        <v>1.07296868949222</v>
+        <v>1.073500603079089</v>
       </c>
       <c r="I184">
-        <v>3.218906068476659</v>
+        <v>3.220501809237266</v>
       </c>
       <c r="J184">
-        <v>261.7399821147321</v>
+        <v>261.8697371151129</v>
       </c>
     </row>
     <row r="185">
@@ -8125,13 +8125,13 @@
         <v>571</v>
       </c>
       <c r="H185">
-        <v>1.07296868949222</v>
+        <v>1.073500603079089</v>
       </c>
       <c r="I185">
-        <v>8.047265171191649</v>
+        <v>8.051254523093164</v>
       </c>
       <c r="J185">
-        <v>612.6651217000575</v>
+        <v>612.9688443581596</v>
       </c>
     </row>
     <row r="186">
@@ -8167,13 +8167,13 @@
         <v>726</v>
       </c>
       <c r="H186">
-        <v>1.07296868949222</v>
+        <v>1.073500603079089</v>
       </c>
       <c r="I186">
-        <v>8.583749515937759</v>
+        <v>8.588004824632709</v>
       </c>
       <c r="J186">
-        <v>778.9752685713516</v>
+        <v>779.3614378354183</v>
       </c>
     </row>
     <row r="187">
@@ -8209,13 +8209,13 @@
         <v>221</v>
       </c>
       <c r="H187">
-        <v>1.07296868949222</v>
+        <v>1.073500603079089</v>
       </c>
       <c r="I187">
-        <v>5.3648434474611</v>
+        <v>5.367503015395442</v>
       </c>
       <c r="J187">
-        <v>237.1260803777806</v>
+        <v>237.2436332804786</v>
       </c>
     </row>
     <row r="188">
@@ -8251,13 +8251,13 @@
         <v>537</v>
       </c>
       <c r="H188">
-        <v>1.07296868949222</v>
+        <v>1.073500603079089</v>
       </c>
       <c r="I188">
-        <v>5.3648434474611</v>
+        <v>5.367503015395442</v>
       </c>
       <c r="J188">
-        <v>576.184186257322</v>
+        <v>576.4698238534705</v>
       </c>
     </row>
     <row r="189">
@@ -8293,13 +8293,13 @@
         <v>98</v>
       </c>
       <c r="H189">
-        <v>1.07296868949222</v>
+        <v>1.073500603079089</v>
       </c>
       <c r="I189">
-        <v>2.68242172373055</v>
+        <v>2.683751507697721</v>
       </c>
       <c r="J189">
-        <v>105.1509315702375</v>
+        <v>105.2030591017507</v>
       </c>
     </row>
     <row r="190">
@@ -8335,13 +8335,13 @@
         <v>98</v>
       </c>
       <c r="H190">
-        <v>1.07296868949222</v>
+        <v>1.073500603079089</v>
       </c>
       <c r="I190">
-        <v>2.68242172373055</v>
+        <v>2.683751507697721</v>
       </c>
       <c r="J190">
-        <v>105.1509315702375</v>
+        <v>105.2030591017507</v>
       </c>
     </row>
     <row r="191">
@@ -8671,13 +8671,13 @@
         <v>243.94</v>
       </c>
       <c r="H198">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I198">
-        <v>3.199238468305995</v>
+        <v>3.199424500507422</v>
       </c>
       <c r="J198">
-        <v>260.1407439861881</v>
+        <v>260.1558708845935</v>
       </c>
     </row>
     <row r="199">
@@ -8713,13 +8713,13 @@
         <v>571</v>
       </c>
       <c r="H199">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I199">
-        <v>7.998096170764986</v>
+        <v>7.998561251268556</v>
       </c>
       <c r="J199">
-        <v>608.9217218009077</v>
+        <v>608.9571299299126</v>
       </c>
     </row>
     <row r="200">
@@ -8755,13 +8755,13 @@
         <v>726</v>
       </c>
       <c r="H200">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I200">
-        <v>8.531302582149319</v>
+        <v>8.531798668019793</v>
       </c>
       <c r="J200">
-        <v>774.2157093300507</v>
+        <v>774.2607291227962</v>
       </c>
     </row>
     <row r="201">
@@ -8797,13 +8797,13 @@
         <v>221</v>
       </c>
       <c r="H201">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I201">
-        <v>5.332064113843325</v>
+        <v>5.33237416751237</v>
       </c>
       <c r="J201">
-        <v>235.6772338318749</v>
+        <v>235.6909382040468</v>
       </c>
     </row>
     <row r="202">
@@ -8839,13 +8839,13 @@
         <v>537</v>
       </c>
       <c r="H202">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I202">
-        <v>5.332064113843325</v>
+        <v>5.33237416751237</v>
       </c>
       <c r="J202">
-        <v>572.6636858267731</v>
+        <v>572.6969855908286</v>
       </c>
     </row>
     <row r="203">
@@ -8881,13 +8881,13 @@
         <v>98</v>
       </c>
       <c r="H203">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I203">
-        <v>2.666032056921662</v>
+        <v>2.666187083756185</v>
       </c>
       <c r="J203">
-        <v>104.5084566313292</v>
+        <v>104.5145336832425</v>
       </c>
     </row>
     <row r="204">
@@ -8923,13 +8923,13 @@
         <v>98</v>
       </c>
       <c r="H204">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I204">
-        <v>2.666032056921662</v>
+        <v>2.666187083756185</v>
       </c>
       <c r="J204">
-        <v>104.5084566313292</v>
+        <v>104.5145336832425</v>
       </c>
     </row>
     <row r="205">
@@ -8965,13 +8965,13 @@
         <v>243.95</v>
       </c>
       <c r="H205">
-        <v>1.012320097102291</v>
+        <v>1.012639839389552</v>
       </c>
       <c r="I205">
-        <v>3.036960291306873</v>
+        <v>3.037919518168657</v>
       </c>
       <c r="J205">
-        <v>246.9554876881039</v>
+        <v>247.0334888190813</v>
       </c>
     </row>
     <row r="206">
@@ -9007,13 +9007,13 @@
         <v>492</v>
       </c>
       <c r="H206">
-        <v>1.012320097102291</v>
+        <v>1.012639839389552</v>
       </c>
       <c r="I206">
-        <v>6.580080631164892</v>
+        <v>6.582158956032091</v>
       </c>
       <c r="J206">
-        <v>498.0614877743272</v>
+        <v>498.2188009796598</v>
       </c>
     </row>
     <row r="207">
@@ -9049,13 +9049,13 @@
         <v>545</v>
       </c>
       <c r="H207">
-        <v>1.012320097102291</v>
+        <v>1.012639839389552</v>
       </c>
       <c r="I207">
-        <v>6.073920582613746</v>
+        <v>6.075839036337314</v>
       </c>
       <c r="J207">
-        <v>551.7144529207486</v>
+        <v>551.888712467306</v>
       </c>
     </row>
     <row r="208">
@@ -9091,13 +9091,13 @@
         <v>177</v>
       </c>
       <c r="H208">
-        <v>1.012320097102291</v>
+        <v>1.012639839389552</v>
       </c>
       <c r="I208">
-        <v>4.049280388409164</v>
+        <v>4.05055935755821</v>
       </c>
       <c r="J208">
-        <v>179.1806571871055</v>
+        <v>179.2372515719508</v>
       </c>
     </row>
     <row r="209">
@@ -9133,13 +9133,13 @@
         <v>376</v>
       </c>
       <c r="H209">
-        <v>1.012320097102291</v>
+        <v>1.012639839389552</v>
       </c>
       <c r="I209">
-        <v>3.543120339858018</v>
+        <v>3.544239437863433</v>
       </c>
       <c r="J209">
-        <v>380.6323565104614</v>
+        <v>380.7525796104717</v>
       </c>
     </row>
     <row r="210">
@@ -9175,13 +9175,13 @@
         <v>78.5</v>
       </c>
       <c r="H210">
-        <v>1.012320097102291</v>
+        <v>1.012639839389552</v>
       </c>
       <c r="I210">
-        <v>2.024640194204582</v>
+        <v>2.025279678779105</v>
       </c>
       <c r="J210">
-        <v>79.46712762252984</v>
+        <v>79.49222739207985</v>
       </c>
     </row>
     <row r="211">
@@ -9217,13 +9217,13 @@
         <v>78.5</v>
       </c>
       <c r="H211">
-        <v>1.012320097102291</v>
+        <v>1.012639839389552</v>
       </c>
       <c r="I211">
-        <v>2.024640194204582</v>
+        <v>2.025279678779105</v>
       </c>
       <c r="J211">
-        <v>79.46712762252984</v>
+        <v>79.49222739207985</v>
       </c>
     </row>
     <row r="212">
@@ -9553,13 +9553,13 @@
         <v>243.95</v>
       </c>
       <c r="H219">
-        <v>1.089495513341624</v>
+        <v>1.089856151631383</v>
       </c>
       <c r="I219">
-        <v>3.268486540024873</v>
+        <v>3.269568454894149</v>
       </c>
       <c r="J219">
-        <v>265.7824304796893</v>
+        <v>265.8704081904759</v>
       </c>
     </row>
     <row r="220">
@@ -9595,13 +9595,13 @@
         <v>492</v>
       </c>
       <c r="H220">
-        <v>1.089495513341624</v>
+        <v>1.089856151631383</v>
       </c>
       <c r="I220">
-        <v>7.081720836720558</v>
+        <v>7.084064985603991</v>
       </c>
       <c r="J220">
-        <v>536.0317925640792</v>
+        <v>536.2092266026406</v>
       </c>
     </row>
     <row r="221">
@@ -9637,13 +9637,13 @@
         <v>545</v>
       </c>
       <c r="H221">
-        <v>1.089495513341624</v>
+        <v>1.089856151631383</v>
       </c>
       <c r="I221">
-        <v>6.536973080049746</v>
+        <v>6.539136909788299</v>
       </c>
       <c r="J221">
-        <v>593.7750547711853</v>
+        <v>593.9716026391038</v>
       </c>
     </row>
     <row r="222">
@@ -9679,13 +9679,13 @@
         <v>177</v>
       </c>
       <c r="H222">
-        <v>1.089495513341624</v>
+        <v>1.089856151631383</v>
       </c>
       <c r="I222">
-        <v>4.357982053366498</v>
+        <v>4.359424606525533</v>
       </c>
       <c r="J222">
-        <v>192.8407058614675</v>
+        <v>192.9045388387548</v>
       </c>
     </row>
     <row r="223">
@@ -9721,13 +9721,13 @@
         <v>376</v>
       </c>
       <c r="H223">
-        <v>1.089495513341624</v>
+        <v>1.089856151631383</v>
       </c>
       <c r="I223">
-        <v>3.813234296695685</v>
+        <v>3.814496530709841</v>
       </c>
       <c r="J223">
-        <v>409.6503130164508</v>
+        <v>409.7859130134001</v>
       </c>
     </row>
     <row r="224">
@@ -9763,13 +9763,13 @@
         <v>78.5</v>
       </c>
       <c r="H224">
-        <v>1.089495513341624</v>
+        <v>1.089856151631383</v>
       </c>
       <c r="I224">
-        <v>2.178991026683249</v>
+        <v>2.179712303262766</v>
       </c>
       <c r="J224">
-        <v>85.52539779731752</v>
+        <v>85.55370790306358</v>
       </c>
     </row>
     <row r="225">
@@ -9805,13 +9805,13 @@
         <v>78.5</v>
       </c>
       <c r="H225">
-        <v>1.089495513341624</v>
+        <v>1.089856151631383</v>
       </c>
       <c r="I225">
-        <v>2.178991026683249</v>
+        <v>2.179712303262766</v>
       </c>
       <c r="J225">
-        <v>85.52539779731752</v>
+        <v>85.55370790306358</v>
       </c>
     </row>
     <row r="226">
@@ -9847,13 +9847,13 @@
         <v>243.94</v>
       </c>
       <c r="H226">
-        <v>1.079311495568228</v>
+        <v>1.079664498716931</v>
       </c>
       <c r="I226">
-        <v>3.237934486704685</v>
+        <v>3.238993496150793</v>
       </c>
       <c r="J226">
-        <v>263.2872462289136</v>
+        <v>263.3733578170082</v>
       </c>
     </row>
     <row r="227">
@@ -9889,13 +9889,13 @@
         <v>571</v>
       </c>
       <c r="H227">
-        <v>1.079311495568228</v>
+        <v>1.079664498716931</v>
       </c>
       <c r="I227">
-        <v>8.094836216761713</v>
+        <v>8.097483740376983</v>
       </c>
       <c r="J227">
-        <v>616.2868639694584</v>
+        <v>616.4884287673676</v>
       </c>
     </row>
     <row r="228">
@@ -9931,13 +9931,13 @@
         <v>726</v>
       </c>
       <c r="H228">
-        <v>1.079311495568228</v>
+        <v>1.079664498716931</v>
       </c>
       <c r="I228">
-        <v>8.634491964545827</v>
+        <v>8.637315989735448</v>
       </c>
       <c r="J228">
-        <v>783.5801457825338</v>
+        <v>783.836426068492</v>
       </c>
     </row>
     <row r="229">
@@ -9973,13 +9973,13 @@
         <v>221</v>
       </c>
       <c r="H229">
-        <v>1.079311495568228</v>
+        <v>1.079664498716931</v>
       </c>
       <c r="I229">
-        <v>5.396557477841142</v>
+        <v>5.398322493584655</v>
       </c>
       <c r="J229">
-        <v>238.5278405205785</v>
+        <v>238.6058542164418</v>
       </c>
     </row>
     <row r="230">
@@ -10015,13 +10015,13 @@
         <v>537</v>
       </c>
       <c r="H230">
-        <v>1.079311495568228</v>
+        <v>1.079664498716931</v>
       </c>
       <c r="I230">
-        <v>5.396557477841142</v>
+        <v>5.398322493584655</v>
       </c>
       <c r="J230">
-        <v>579.5902731201386</v>
+        <v>579.7798358109919</v>
       </c>
     </row>
     <row r="231">
@@ -10057,13 +10057,13 @@
         <v>98</v>
       </c>
       <c r="H231">
-        <v>1.079311495568228</v>
+        <v>1.079664498716931</v>
       </c>
       <c r="I231">
-        <v>2.698278738920571</v>
+        <v>2.699161246792328</v>
       </c>
       <c r="J231">
-        <v>105.7725265656864</v>
+        <v>105.8071208742592</v>
       </c>
     </row>
     <row r="232">
@@ -10099,13 +10099,13 @@
         <v>98</v>
       </c>
       <c r="H232">
-        <v>1.079311495568228</v>
+        <v>1.079664498716931</v>
       </c>
       <c r="I232">
-        <v>2.698278738920571</v>
+        <v>2.699161246792328</v>
       </c>
       <c r="J232">
-        <v>105.7725265656864</v>
+        <v>105.8071208742592</v>
       </c>
     </row>
     <row r="233">
@@ -10141,13 +10141,13 @@
         <v>243.95</v>
       </c>
       <c r="H233">
-        <v>0.9903137179476618</v>
+        <v>0.9903664008368738</v>
       </c>
       <c r="I233">
-        <v>2.970941153842985</v>
+        <v>2.971099202510621</v>
       </c>
       <c r="J233">
-        <v>241.5870314933321</v>
+        <v>241.5998834841554</v>
       </c>
     </row>
     <row r="234">
@@ -10183,13 +10183,13 @@
         <v>492</v>
       </c>
       <c r="H234">
-        <v>0.9903137179476618</v>
+        <v>0.9903664008368738</v>
       </c>
       <c r="I234">
-        <v>6.437039166659801</v>
+        <v>6.437381605439679</v>
       </c>
       <c r="J234">
-        <v>487.2343492302496</v>
+        <v>487.2602692117419</v>
       </c>
     </row>
     <row r="235">
@@ -10225,13 +10225,13 @@
         <v>545</v>
       </c>
       <c r="H235">
-        <v>0.9903137179476618</v>
+        <v>0.9903664008368738</v>
       </c>
       <c r="I235">
-        <v>5.941882307685971</v>
+        <v>5.942198405021243</v>
       </c>
       <c r="J235">
-        <v>539.7209762814757</v>
+        <v>539.7496884560962</v>
       </c>
     </row>
     <row r="236">
@@ -10267,13 +10267,13 @@
         <v>177</v>
       </c>
       <c r="H236">
-        <v>0.9903137179476618</v>
+        <v>0.9903664008368738</v>
       </c>
       <c r="I236">
-        <v>3.961254871790647</v>
+        <v>3.961465603347495</v>
       </c>
       <c r="J236">
-        <v>175.2855280767361</v>
+        <v>175.2948529481266</v>
       </c>
     </row>
     <row r="237">
@@ -10309,13 +10309,13 @@
         <v>376</v>
       </c>
       <c r="H237">
-        <v>0.9903137179476618</v>
+        <v>0.9903664008368738</v>
       </c>
       <c r="I237">
-        <v>3.466098012816816</v>
+        <v>3.466282402929058</v>
       </c>
       <c r="J237">
-        <v>372.3579579483208</v>
+        <v>372.3777667146645</v>
       </c>
     </row>
     <row r="238">
@@ -10351,13 +10351,13 @@
         <v>78.5</v>
       </c>
       <c r="H238">
-        <v>0.9903137179476618</v>
+        <v>0.9903664008368738</v>
       </c>
       <c r="I238">
-        <v>1.980627435895324</v>
+        <v>1.980732801673748</v>
       </c>
       <c r="J238">
-        <v>77.73962685889146</v>
+        <v>77.74376246569459</v>
       </c>
     </row>
     <row r="239">
@@ -10393,13 +10393,13 @@
         <v>78.5</v>
       </c>
       <c r="H239">
-        <v>0.9903137179476618</v>
+        <v>0.9903664008368738</v>
       </c>
       <c r="I239">
-        <v>1.980627435895324</v>
+        <v>1.980732801673748</v>
       </c>
       <c r="J239">
-        <v>77.73962685889146</v>
+        <v>77.74376246569459</v>
       </c>
     </row>
     <row r="240">
@@ -10435,13 +10435,13 @@
         <v>243.94</v>
       </c>
       <c r="H240">
-        <v>1.043278788403571</v>
+        <v>1.043763788270815</v>
       </c>
       <c r="I240">
-        <v>3.129836365210713</v>
+        <v>3.131291364812444</v>
       </c>
       <c r="J240">
-        <v>254.4974276431671</v>
+        <v>254.6157385107826</v>
       </c>
     </row>
     <row r="241">
@@ -10477,13 +10477,13 @@
         <v>571</v>
       </c>
       <c r="H241">
-        <v>1.043278788403571</v>
+        <v>1.043763788270815</v>
       </c>
       <c r="I241">
-        <v>7.824590913026783</v>
+        <v>7.828228412031112</v>
       </c>
       <c r="J241">
-        <v>595.7121881784391</v>
+        <v>595.9891231026353</v>
       </c>
     </row>
     <row r="242">
@@ -10519,13 +10519,13 @@
         <v>726</v>
       </c>
       <c r="H242">
-        <v>1.043278788403571</v>
+        <v>1.043763788270815</v>
       </c>
       <c r="I242">
-        <v>8.346230307228568</v>
+        <v>8.350110306166519</v>
       </c>
       <c r="J242">
-        <v>757.4204003809925</v>
+        <v>757.7725102846116</v>
       </c>
     </row>
     <row r="243">
@@ -10561,13 +10561,13 @@
         <v>221</v>
       </c>
       <c r="H243">
-        <v>1.043278788403571</v>
+        <v>1.043763788270815</v>
       </c>
       <c r="I243">
-        <v>5.216393942017855</v>
+        <v>5.218818941354074</v>
       </c>
       <c r="J243">
-        <v>230.5646122371892</v>
+        <v>230.6717972078501</v>
       </c>
     </row>
     <row r="244">
@@ -10603,13 +10603,13 @@
         <v>537</v>
       </c>
       <c r="H244">
-        <v>1.043278788403571</v>
+        <v>1.043763788270815</v>
       </c>
       <c r="I244">
-        <v>5.216393942017855</v>
+        <v>5.218818941354074</v>
       </c>
       <c r="J244">
-        <v>560.2407093727177</v>
+        <v>560.5011543014276</v>
       </c>
     </row>
     <row r="245">
@@ -10645,13 +10645,13 @@
         <v>98</v>
       </c>
       <c r="H245">
-        <v>1.043278788403571</v>
+        <v>1.043763788270815</v>
       </c>
       <c r="I245">
-        <v>2.608196971008927</v>
+        <v>2.609409470677037</v>
       </c>
       <c r="J245">
-        <v>102.24132126355</v>
+        <v>102.2888512505398</v>
       </c>
     </row>
     <row r="246">
@@ -10687,13 +10687,13 @@
         <v>98</v>
       </c>
       <c r="H246">
-        <v>1.043278788403571</v>
+        <v>1.043763788270815</v>
       </c>
       <c r="I246">
-        <v>2.608196971008927</v>
+        <v>2.609409470677037</v>
       </c>
       <c r="J246">
-        <v>102.24132126355</v>
+        <v>102.2888512505398</v>
       </c>
     </row>
     <row r="247">
@@ -11023,13 +11023,13 @@
         <v>243.94</v>
       </c>
       <c r="H254">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I254">
-        <v>3.199238468305995</v>
+        <v>3.199424500507422</v>
       </c>
       <c r="J254">
-        <v>260.1407439861881</v>
+        <v>260.1558708845935</v>
       </c>
     </row>
     <row r="255">
@@ -11065,13 +11065,13 @@
         <v>571</v>
       </c>
       <c r="H255">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I255">
-        <v>7.998096170764986</v>
+        <v>7.998561251268556</v>
       </c>
       <c r="J255">
-        <v>608.9217218009077</v>
+        <v>608.9571299299126</v>
       </c>
     </row>
     <row r="256">
@@ -11107,13 +11107,13 @@
         <v>726</v>
       </c>
       <c r="H256">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I256">
-        <v>8.531302582149319</v>
+        <v>8.531798668019793</v>
       </c>
       <c r="J256">
-        <v>774.2157093300507</v>
+        <v>774.2607291227962</v>
       </c>
     </row>
     <row r="257">
@@ -11149,13 +11149,13 @@
         <v>221</v>
       </c>
       <c r="H257">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I257">
-        <v>5.332064113843325</v>
+        <v>5.33237416751237</v>
       </c>
       <c r="J257">
-        <v>235.6772338318749</v>
+        <v>235.6909382040468</v>
       </c>
     </row>
     <row r="258">
@@ -11191,13 +11191,13 @@
         <v>537</v>
       </c>
       <c r="H258">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I258">
-        <v>5.332064113843325</v>
+        <v>5.33237416751237</v>
       </c>
       <c r="J258">
-        <v>572.6636858267731</v>
+        <v>572.6969855908286</v>
       </c>
     </row>
     <row r="259">
@@ -11233,13 +11233,13 @@
         <v>98</v>
       </c>
       <c r="H259">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I259">
-        <v>2.666032056921662</v>
+        <v>2.666187083756185</v>
       </c>
       <c r="J259">
-        <v>104.5084566313292</v>
+        <v>104.5145336832425</v>
       </c>
     </row>
     <row r="260">
@@ -11275,13 +11275,13 @@
         <v>98</v>
       </c>
       <c r="H260">
-        <v>1.066412822768665</v>
+        <v>1.066474833502474</v>
       </c>
       <c r="I260">
-        <v>2.666032056921662</v>
+        <v>2.666187083756185</v>
       </c>
       <c r="J260">
-        <v>104.5084566313292</v>
+        <v>104.5145336832425</v>
       </c>
     </row>
     <row r="261">
@@ -11317,13 +11317,13 @@
         <v>243.95</v>
       </c>
       <c r="H261">
-        <v>1.008898311530522</v>
+        <v>1.008924278049152</v>
       </c>
       <c r="I261">
-        <v>3.026694934591566</v>
+        <v>3.026772834147455</v>
       </c>
       <c r="J261">
-        <v>246.1207430978708</v>
+        <v>246.1270776300906</v>
       </c>
     </row>
     <row r="262">
@@ -11359,13 +11359,13 @@
         <v>492</v>
       </c>
       <c r="H262">
-        <v>1.008898311530522</v>
+        <v>1.008924278049152</v>
       </c>
       <c r="I262">
-        <v>6.557839024948392</v>
+        <v>6.558007807319487</v>
       </c>
       <c r="J262">
-        <v>496.3779692730168</v>
+        <v>496.3907448001827</v>
       </c>
     </row>
     <row r="263">
@@ -11401,13 +11401,13 @@
         <v>545</v>
       </c>
       <c r="H263">
-        <v>1.008898311530522</v>
+        <v>1.008924278049152</v>
       </c>
       <c r="I263">
-        <v>6.053389869183132</v>
+        <v>6.053545668294911</v>
       </c>
       <c r="J263">
-        <v>549.8495797841344</v>
+        <v>549.8637315367878</v>
       </c>
     </row>
     <row r="264">
@@ -11443,13 +11443,13 @@
         <v>177</v>
       </c>
       <c r="H264">
-        <v>1.008898311530522</v>
+        <v>1.008924278049152</v>
       </c>
       <c r="I264">
-        <v>4.035593246122088</v>
+        <v>4.035697112196607</v>
       </c>
       <c r="J264">
-        <v>178.5750011409024</v>
+        <v>178.5795972146999</v>
       </c>
     </row>
     <row r="265">
@@ -11485,13 +11485,13 @@
         <v>376</v>
       </c>
       <c r="H265">
-        <v>1.008898311530522</v>
+        <v>1.008924278049152</v>
       </c>
       <c r="I265">
-        <v>3.531144090356827</v>
+        <v>3.531234973172031</v>
       </c>
       <c r="J265">
-        <v>379.3457651354763</v>
+        <v>379.3555285464811</v>
       </c>
     </row>
     <row r="266">
@@ -11527,13 +11527,13 @@
         <v>78.5</v>
       </c>
       <c r="H266">
-        <v>1.008898311530522</v>
+        <v>1.008924278049152</v>
       </c>
       <c r="I266">
-        <v>2.017796623061044</v>
+        <v>2.017848556098304</v>
       </c>
       <c r="J266">
-        <v>79.19851745514597</v>
+        <v>79.20055582685842</v>
       </c>
     </row>
     <row r="267">
@@ -11569,13 +11569,13 @@
         <v>78.5</v>
       </c>
       <c r="H267">
-        <v>1.008898311530522</v>
+        <v>1.008924278049152</v>
       </c>
       <c r="I267">
-        <v>2.017796623061044</v>
+        <v>2.017848556098304</v>
       </c>
       <c r="J267">
-        <v>79.19851745514597</v>
+        <v>79.20055582685842</v>
       </c>
     </row>
     <row r="268">
